--- a/artfynd/A 26374-2023 artfynd.xlsx
+++ b/artfynd/A 26374-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178092</v>
+        <v>113178094</v>
       </c>
       <c r="B2" t="n">
-        <v>90689</v>
+        <v>90045</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566615</v>
+        <v>566697</v>
       </c>
       <c r="R2" t="n">
-        <v>7027352</v>
+        <v>7027356</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,11 +768,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178093</v>
+        <v>113178091</v>
       </c>
       <c r="B3" t="n">
-        <v>90029</v>
+        <v>90063</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566629</v>
+        <v>566616</v>
       </c>
       <c r="R3" t="n">
-        <v>7027352</v>
+        <v>7027340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,15 +883,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # på levande gammal gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178091</v>
+        <v>113178092</v>
       </c>
       <c r="B4" t="n">
-        <v>90047</v>
+        <v>90705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>898</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566616</v>
+        <v>566615</v>
       </c>
       <c r="R4" t="n">
-        <v>7027340</v>
+        <v>7027352</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178094</v>
+        <v>113178093</v>
       </c>
       <c r="B5" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566697</v>
+        <v>566629</v>
       </c>
       <c r="R5" t="n">
-        <v>7027356</v>
+        <v>7027352</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 26374-2023 artfynd.xlsx
+++ b/artfynd/A 26374-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178094</v>
+        <v>113178093</v>
       </c>
       <c r="B2" t="n">
         <v>90045</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566697</v>
+        <v>566629</v>
       </c>
       <c r="R2" t="n">
-        <v>7027356</v>
+        <v>7027352</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178092</v>
+        <v>113178094</v>
       </c>
       <c r="B4" t="n">
-        <v>90705</v>
+        <v>90045</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566615</v>
+        <v>566697</v>
       </c>
       <c r="R4" t="n">
-        <v>7027352</v>
+        <v>7027356</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,11 +1006,11 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178093</v>
+        <v>113178092</v>
       </c>
       <c r="B5" t="n">
-        <v>90045</v>
+        <v>90705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,25 +1044,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566629</v>
+        <v>566615</v>
       </c>
       <c r="R5" t="n">
         <v>7027352</v>
@@ -1125,11 +1125,11 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 26374-2023 artfynd.xlsx
+++ b/artfynd/A 26374-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178093</v>
+        <v>113178094</v>
       </c>
       <c r="B2" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566629</v>
+        <v>566697</v>
       </c>
       <c r="R2" t="n">
-        <v>7027352</v>
+        <v>7027356</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -797,7 +797,7 @@
         <v>113178091</v>
       </c>
       <c r="B3" t="n">
-        <v>90063</v>
+        <v>90075</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178094</v>
+        <v>113178093</v>
       </c>
       <c r="B4" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566697</v>
+        <v>566629</v>
       </c>
       <c r="R4" t="n">
-        <v>7027356</v>
+        <v>7027352</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1035,7 +1035,7 @@
         <v>113178092</v>
       </c>
       <c r="B5" t="n">
-        <v>90705</v>
+        <v>90717</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 26374-2023 artfynd.xlsx
+++ b/artfynd/A 26374-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178094</v>
+        <v>113178092</v>
       </c>
       <c r="B2" t="n">
-        <v>90057</v>
+        <v>90717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566697</v>
+        <v>566615</v>
       </c>
       <c r="R2" t="n">
-        <v>7027356</v>
+        <v>7027352</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,11 +768,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178091</v>
+        <v>113178094</v>
       </c>
       <c r="B3" t="n">
-        <v>90075</v>
+        <v>90057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566616</v>
+        <v>566697</v>
       </c>
       <c r="R3" t="n">
-        <v>7027340</v>
+        <v>7027356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,15 +883,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178093</v>
+        <v>113178091</v>
       </c>
       <c r="B4" t="n">
-        <v>90057</v>
+        <v>90075</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566629</v>
+        <v>566616</v>
       </c>
       <c r="R4" t="n">
-        <v>7027352</v>
+        <v>7027340</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,15 +1002,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # på levande gammal gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178092</v>
+        <v>113178093</v>
       </c>
       <c r="B5" t="n">
-        <v>90717</v>
+        <v>90057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,25 +1044,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566615</v>
+        <v>566629</v>
       </c>
       <c r="R5" t="n">
         <v>7027352</v>
@@ -1125,11 +1125,11 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 26374-2023 artfynd.xlsx
+++ b/artfynd/A 26374-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178092</v>
+        <v>113178093</v>
       </c>
       <c r="B2" t="n">
-        <v>90717</v>
+        <v>90079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566615</v>
+        <v>566629</v>
       </c>
       <c r="R2" t="n">
         <v>7027352</v>
@@ -768,11 +768,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178094</v>
+        <v>113178092</v>
       </c>
       <c r="B3" t="n">
-        <v>90057</v>
+        <v>90739</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566697</v>
+        <v>566615</v>
       </c>
       <c r="R3" t="n">
-        <v>7027356</v>
+        <v>7027352</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178091</v>
+        <v>113178094</v>
       </c>
       <c r="B4" t="n">
-        <v>90075</v>
+        <v>90079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566616</v>
+        <v>566697</v>
       </c>
       <c r="R4" t="n">
-        <v>7027340</v>
+        <v>7027356</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,15 +1002,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178093</v>
+        <v>113178091</v>
       </c>
       <c r="B5" t="n">
-        <v>90057</v>
+        <v>90097</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566629</v>
+        <v>566616</v>
       </c>
       <c r="R5" t="n">
-        <v>7027352</v>
+        <v>7027340</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,15 +1121,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # på levande gammal gran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 26374-2023 artfynd.xlsx
+++ b/artfynd/A 26374-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113178093</v>
       </c>
       <c r="B2" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>113178092</v>
       </c>
       <c r="B3" t="n">
-        <v>90739</v>
+        <v>90743</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178094</v>
+        <v>113178091</v>
       </c>
       <c r="B4" t="n">
-        <v>90079</v>
+        <v>90101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566697</v>
+        <v>566616</v>
       </c>
       <c r="R4" t="n">
-        <v>7027356</v>
+        <v>7027340</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,15 +1002,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # på levande gammal gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178091</v>
+        <v>113178094</v>
       </c>
       <c r="B5" t="n">
-        <v>90097</v>
+        <v>90083</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566616</v>
+        <v>566697</v>
       </c>
       <c r="R5" t="n">
-        <v>7027340</v>
+        <v>7027356</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,15 +1121,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 26374-2023 artfynd.xlsx
+++ b/artfynd/A 26374-2023 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178092</v>
+        <v>113178091</v>
       </c>
       <c r="B3" t="n">
-        <v>90743</v>
+        <v>90101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>898</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566615</v>
+        <v>566616</v>
       </c>
       <c r="R3" t="n">
-        <v>7027352</v>
+        <v>7027340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>1 substratenheter # på levande gammal gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178091</v>
+        <v>113178092</v>
       </c>
       <c r="B4" t="n">
-        <v>90101</v>
+        <v>90743</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>898</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566616</v>
+        <v>566615</v>
       </c>
       <c r="R4" t="n">
-        <v>7027340</v>
+        <v>7027352</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 26374-2023 artfynd.xlsx
+++ b/artfynd/A 26374-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26374-2023 artfynd.xlsx
+++ b/artfynd/A 26374-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178093</v>
+        <v>113178092</v>
       </c>
       <c r="B2" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566629</v>
+        <v>566615</v>
       </c>
       <c r="R2" t="n">
         <v>7027352</v>
@@ -768,11 +763,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178092</v>
+        <v>113178093</v>
       </c>
       <c r="B3" t="n">
-        <v>90997</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,7 +824,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566615</v>
+        <v>566629</v>
       </c>
       <c r="R3" t="n">
         <v>7027352</v>
@@ -887,11 +877,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178091</v>
+        <v>113178094</v>
       </c>
       <c r="B4" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566615</v>
+        <v>566697</v>
       </c>
       <c r="R4" t="n">
-        <v>7027340</v>
+        <v>7027356</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,15 +987,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1025,125 +1010,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>113178094</v>
-      </c>
-      <c r="B5" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Fjällbohög, söder om täkterna, Ång</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>566697</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7027356</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Edsele</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 26374-2023 artfynd.xlsx
+++ b/artfynd/A 26374-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178092</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178093</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,8 +1029,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178094</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>